--- a/docs/xlsx/jobs-2026-08-29.xlsx
+++ b/docs/xlsx/jobs-2026-08-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -59,6 +59,96 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/9327559dd951481fa7372550da6b030a-advocacy-and-policy-manager-asian-american-federation-new-york</t>
+  </si>
+  <si>
+    <t>Coordinator, Disaster Response (Preference for Minnesota)</t>
+  </si>
+  <si>
+    <t>NECHAMA - Jewish Response to Disaster</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Disaster Relief, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b413d47d8d6436e9f17373d7be333c1-coordinator-disaster-response-preference-for-minnesota-nechama-jewish-response-to-disaster-saint-paul</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Peace Community Center-Tacoma</t>
+  </si>
+  <si>
+    <t>Tacoma, WA</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71676967edd0421b8fbb69d25696246e-executive-director-peace-community-center-tacoma-tacoma</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Temecula, CA</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 23.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b078719ab044cdc8e9944d467a10bab-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-temecula</t>
+  </si>
+  <si>
+    <t>Manager for Disaster Response: Mitigation, Preparedness &amp; Long-term Recovery (Preference for Minnesota)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Rural Areas, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e28209f390b644b7ae001e548de2d375-manager-for-disaster-response-mitigation-preparedness-long-term-recovery-preference-for-minnesota-nechama-jewish-response-to-disaster-saint-paul</t>
+  </si>
+  <si>
+    <t>TK-6 ELEMENTARY BUSINESS MANAGER</t>
+  </si>
+  <si>
+    <t>Walden Center &amp; School</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 60015.78 - 60015.78/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28aac8a833654f14aa8ca0ccf5c713f4-tk-6-elementary-business-manager-walden-center-school-berkeley</t>
   </si>
 </sst>
 </file>
@@ -540,7 +630,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -602,10 +692,130 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-29.xlsx
+++ b/docs/xlsx/jobs-2026-08-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="56">
   <si>
     <t>Title</t>
   </si>
@@ -130,6 +130,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/e28209f390b644b7ae001e548de2d375-manager-for-disaster-response-mitigation-preparedness-long-term-recovery-preference-for-minnesota-nechama-jewish-response-to-disaster-saint-paul</t>
   </si>
   <si>
+    <t>Mental Health Clinical Coordinator &amp; Supervisor</t>
+  </si>
+  <si>
+    <t>What's Up Wellness</t>
+  </si>
+  <si>
+    <t>Grass Valley, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 62.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c18d0f5831e44a758e9d70d28454c50d-mental-health-clinical-coordinator-supervisor-whats-up-wellness-grass-valley</t>
+  </si>
+  <si>
     <t>TK-6 ELEMENTARY BUSINESS MANAGER</t>
   </si>
   <si>
@@ -139,9 +160,6 @@
     <t>Berkeley, California</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 60015.78 - 60015.78/year</t>
   </si>
   <si>
@@ -149,6 +167,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/28aac8a833654f14aa8ca0ccf5c713f4-tk-6-elementary-business-manager-walden-center-school-berkeley</t>
+  </si>
+  <si>
+    <t>Virtual Assistant / Intake Specialist</t>
+  </si>
+  <si>
+    <t>Esperanza, Inc.</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 29.00/year</t>
+  </si>
+  <si>
+    <t>Education, Race Ethnicity, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc8d842262104d5690e99cdca004ae92-virtual-assistant-intake-specialist-esperanza-inc-cleveland</t>
   </si>
 </sst>
 </file>
@@ -630,7 +663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -807,6 +840,52 @@
         <v>44</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
@@ -816,6 +895,8 @@
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
     <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
